--- a/artfynd/A 69109-2021 artfynd.xlsx
+++ b/artfynd/A 69109-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69109-2021 artfynd.xlsx
+++ b/artfynd/A 69109-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62062021</v>
+        <v>69568820</v>
       </c>
       <c r="B2" t="n">
-        <v>90282</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4740</v>
+        <v>2697</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Nordlig tuffmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Palustriella decipiens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(De Not.) Ochyra</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jormliklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450967.7506964616</v>
+        <v>450941</v>
       </c>
       <c r="R2" t="n">
-        <v>7179045.019876677</v>
+        <v>7179009</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Jormliklumpens sydsluttning, ca 400 m norr om Jormliens Fjällgård,</t>
+          <t>2017-07-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,35 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre fjällnära barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Henrik Weibull, Elvira Weibull, Elias Weibull, Anki Weibull</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69568820</v>
+        <v>62062021</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2697</v>
+        <v>4740</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordlig tuffmossa</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Palustriella decipiens</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(De Not.) Ochyra</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jormliklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450941.48506224</v>
+        <v>450968</v>
       </c>
       <c r="R3" t="n">
-        <v>7179008.691005521</v>
+        <v>7179045</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Jormliklumpens sydsluttning, ca 400 m norr om Jormliens Fjällgård,</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,36 +868,30 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre fjällnära barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Elvira Weibull, Elias Weibull, Anki Weibull</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82562967</v>
+        <v>59823666</v>
       </c>
       <c r="B4" t="n">
-        <v>101854</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,37 +899,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220461</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jormliklumpen, Jmt</t>
+          <t>Jormliklumpens sydsluttning, ca 650 m nordnordväst om Jormliens Fjällgård,, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450941.48506224</v>
+        <v>450785</v>
       </c>
       <c r="R4" t="n">
-        <v>7179008.691005521</v>
+        <v>7179216</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +953,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-07-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-07-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-07-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-07-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,24 +974,223 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre fjällnära barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>82562967</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104803</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220461</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsbräsma</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cardamine flexuosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jormliklumpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>450941</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7179009</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-07-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-07-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre fjällnära barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Henrik Weibull, Elvira Weibull, Elias Weibull, Anki Weibull</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>61195916</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98234</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222759</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Taggbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polystichum lonchitis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jormliklumpens sydsluttning, ca 650 m nordnordväst om Jormliens Fjällgård,, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>450785</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7179216</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2006-07-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2006-07-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69109-2021 artfynd.xlsx
+++ b/artfynd/A 69109-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69568820</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62062021</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59823666</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82562967</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,8 +1216,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61195916</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>